--- a/iuh/môn/hk2-3/trien-khai-anht/gk/Tổng hợp IP hiện tại và CARP.xlsx
+++ b/iuh/môn/hk2-3/trien-khai-anht/gk/Tổng hợp IP hiện tại và CARP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\folder\rac\iuh\môn\hk2-3\trien-khai-anht\gk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB76D28-BB3D-48D3-8CB8-BCA559932ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BAC89DB-6225-492E-820F-0B89B7205354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="69">
   <si>
     <t>(Không có)</t>
   </si>
@@ -584,6 +584,154 @@
   </si>
   <si>
     <t xml:space="preserve">🌟 IP ẢO (VIP) dùng làm gateway nếu làm carp , trừ cái wan1 để truy cập web </t>
+  </si>
+  <si>
+    <t>Vùng mạng Site B</t>
+  </si>
+  <si>
+    <t>IP pfSense 3</t>
+  </si>
+  <si>
+    <t>WAN (Internet)</t>
+  </si>
+  <si>
+    <r>
+      <t>VMnet 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Để đi chung đường với Site A)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>192.168.137.20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> /24</t>
+    </r>
+  </si>
+  <si>
+    <t>192.168.137.1</t>
+  </si>
+  <si>
+    <t>LAN (Nội bộ)</t>
+  </si>
+  <si>
+    <r>
+      <t>VMnet 15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Tạo đại 1 mạng mới)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>192.168.15.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> /24</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ubuntu VPN:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>192.168.15.10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">(Trỏ GW về </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>192.168.15.1</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -726,7 +874,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
@@ -751,24 +899,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -777,6 +907,42 @@
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1001,7 +1167,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
@@ -1012,7 +1178,7 @@
     <col min="6" max="6" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="26.25" thickBot="1">
+    <row r="1" spans="1:6" ht="13.5" thickBot="1">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -1053,19 +1219,19 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="12.75">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="14" t="s">
         <v>12</v>
       </c>
       <c r="F3" s="7" t="s">
@@ -1073,37 +1239,37 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="12.75">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="10"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="15"/>
       <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:6" ht="47.25" customHeight="1" thickBot="1">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="11"/>
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="16"/>
       <c r="F5" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="14" t="s">
         <v>12</v>
       </c>
       <c r="F6" s="7" t="s">
@@ -1111,40 +1277,40 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="10"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="15"/>
       <c r="F7" s="8"/>
     </row>
     <row r="8" spans="1:6" ht="47.25" customHeight="1" thickBot="1">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="11"/>
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="16"/>
       <c r="F8" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="32.25" customHeight="1" thickBot="1">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="15"/>
+      <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" thickBot="1"/>
     <row r="11" spans="1:6" ht="46.5" customHeight="1" thickBot="1">
@@ -1180,7 +1346,7 @@
       <c r="D12" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="12" t="s">
         <v>41</v>
       </c>
       <c r="F12" s="6" t="s">
@@ -1200,7 +1366,7 @@
       <c r="D13" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="13" t="s">
         <v>46</v>
       </c>
       <c r="F13" s="6" t="s">
@@ -1211,7 +1377,7 @@
       <c r="A14" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="13" t="s">
         <v>47</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -1220,7 +1386,7 @@
       <c r="D14" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="12" t="s">
         <v>50</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -1231,7 +1397,7 @@
       <c r="A15" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="13" t="s">
         <v>47</v>
       </c>
       <c r="C15" s="4" t="s">
@@ -1240,15 +1406,87 @@
       <c r="D15" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="12" t="s">
         <v>54</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>55</v>
       </c>
     </row>
+    <row r="16" spans="1:6" ht="15.75" customHeight="1" thickBot="1"/>
+    <row r="17" spans="1:5" ht="47.25" customHeight="1" thickBot="1">
+      <c r="A17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="34.5" customHeight="1" thickBot="1">
+      <c r="A18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A19" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A20" s="15"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="8"/>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="14">
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>

--- a/iuh/môn/hk2-3/trien-khai-anht/gk/Tổng hợp IP hiện tại và CARP.xlsx
+++ b/iuh/môn/hk2-3/trien-khai-anht/gk/Tổng hợp IP hiện tại và CARP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\folder\rac\iuh\môn\hk2-3\trien-khai-anht\gk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BAC89DB-6225-492E-820F-0B89B7205354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34361953-0291-4F7B-BD67-197208AB3AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="70">
   <si>
     <t>(Không có)</t>
   </si>
@@ -732,6 +732,9 @@
       </rPr>
       <t>)</t>
     </r>
+  </si>
+  <si>
+    <t>ubuntu -zabbix - 172.16.0.20</t>
   </si>
 </sst>
 </file>
@@ -918,6 +921,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
@@ -925,24 +946,6 @@
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1225,10 +1228,10 @@
       <c r="B3" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="23" t="s">
         <v>20</v>
       </c>
       <c r="E3" s="14" t="s">
@@ -1241,16 +1244,18 @@
     <row r="4" spans="1:6" ht="12.75">
       <c r="A4" s="15"/>
       <c r="B4" s="15"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
       <c r="E4" s="15"/>
-      <c r="F4" s="8"/>
+      <c r="F4" s="8" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="5" spans="1:6" ht="47.25" customHeight="1" thickBot="1">
       <c r="A5" s="16"/>
       <c r="B5" s="16"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
       <c r="E5" s="16"/>
       <c r="F5" s="2" t="s">
         <v>29</v>
@@ -1263,10 +1268,10 @@
       <c r="B6" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="23" t="s">
         <v>21</v>
       </c>
       <c r="E6" s="14" t="s">
@@ -1279,16 +1284,16 @@
     <row r="7" spans="1:6" ht="15.75" customHeight="1">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
       <c r="E7" s="15"/>
       <c r="F7" s="8"/>
     </row>
     <row r="8" spans="1:6" ht="47.25" customHeight="1" thickBot="1">
       <c r="A8" s="16"/>
       <c r="B8" s="16"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
       <c r="E8" s="16"/>
       <c r="F8" s="2" t="s">
         <v>28</v>
@@ -1455,10 +1460,10 @@
       <c r="B19" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="C19" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D19" s="23" t="s">
+      <c r="D19" s="20" t="s">
         <v>47</v>
       </c>
       <c r="E19" s="7" t="s">
@@ -1468,21 +1473,28 @@
     <row r="20" spans="1:5" ht="15.75" customHeight="1">
       <c r="A20" s="15"/>
       <c r="B20" s="15"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="24"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="21"/>
       <c r="E20" s="8"/>
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="16"/>
       <c r="B21" s="16"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="25"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="22"/>
       <c r="E21" s="2" t="s">
         <v>68</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="D6:D8"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="C19:C21"/>
@@ -1490,13 +1502,6 @@
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="D6:D8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
